--- a/_historico/merge/candidatos.xlsx
+++ b/_historico/merge/candidatos.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidatos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatos'!$A$1:$R$496</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatos'!$A$1:$R$579</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R496"/>
+  <dimension ref="A1:R579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,92 +439,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Chave</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ID FGV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Nome Empresa</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CNPJ</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>UF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Data coleta</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FONTE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PRODUTO PESQUISADO</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Preço lido</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Preço pela regra</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>VALOR FRETE</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>OBS FRETE (origem)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Situação</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Sugestão</t>
         </is>
@@ -40747,8 +40735,6619 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1001|1</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>GUARULHOS DISTRIBUIDORA DE EMBALAGENS LTDA (Guarulhos Embalagens)</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>30.679.614/0001-02</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>https://www.guarulhosembalagens.com.br/produtos-de-limpeza/alcool-liquido-5-litros</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>Alcool Liquido 5 Litros</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>47.78</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: CORREIOS PAC R$ 47,78 Previsto para 23/10/2026 até 27/10/2026</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1001_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: álcool 70% INPM (descrição da página); o insumo é álcool 46,2°</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1002|1</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/alcool-em-gel-antisseptico/alcool-em-gel-kimbra-70-antisseptico-5l-1-un/?PID=81051</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Álcool em Gel Kimbra 70% Antisséptico 5L 1 UN</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>48.96</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 48,96 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1002_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: álcool em gel; o insumo é álcool líquido</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1002|2</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>H D DISTRIBUIDORA DE PRODUTOS HIGIENICOS E DESCARTAVEIS LTDA (HD Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>03.868.183/0001-50</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>https://hddistribuidora.com/produto/alcool-70-5-litros/</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Álcool 70% Facilita 5 Litros – Uso Profissional</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>58.09</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Melhor Envio) (5 a 7 dias úteis): R$58,09</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1002_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1008|1</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/cera-liquida-2l-incolor-polylar</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Cera Liquida 2L Incolor - Polylar</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>13.29</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>48.91</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 48,91 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1008_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1009|1</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/cera-liquida-750ml-vermelha-polylar</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Cera Liquida 750ml Vermelha - Polylar</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>40.78</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 40,78 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1009_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: cera para pisos laváveis (a página desaconselha laminado de madeira); o insumo é cera específica para madeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1009|2</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/cera-liquida-girando-sol-incolor-750ml.html</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Cera Líquida Girando Sol Incolor 750ml</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>10.43</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>37.54</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 37,54 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1009_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: cera para pisos em geral, não específica para madeira (o mesmo produto já está no 1008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1009|4</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/cera-automotiva-liquida-5-litros-valencia</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Cera Automotiva Líquida 5 Litros Valência</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 35,75 7 dias úteis Jadlog Package</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1009_GO_4.png</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: cera automotiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1011|1</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>H D DISTRIBUIDORA DE PRODUTOS HIGIENICOS E DESCARTAVEIS LTDA (HD Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>03.868.183/0001-50</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>https://hddistribuidora.com/produto/desinfetante-hospitalar-concentrado-easy-2-dose-master-oxy-ac-health-5l-oxigenio-ativo/</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Desinfetante Hospitalar Concentrado Easy 2 Dose Master Oxy AC Health 5L Oxigênio Ativo</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Melhor Envio) (5 a 7 dias úteis): R$62,63</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1011_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: desinfetante à base de oxigênio ativo; o insumo é à base de quaternário de amônio</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1012|1</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/pedras-sanitarias/desodorizador-sanitario-pato-gel-adesivo-com-6-discos-e-aplicador-marine-1-un/?PID=22302</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Desodorizador Sanitário Pato Gel Adesivo com 6 Discos e Aplicador Marine 1 UN</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>30.43</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,43 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1012_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: gel adesivo em discos; o insumo é pedra sanitária com rede protetora e gancho</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1013|1</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/pedras-sanitarias/desodorizador-sanitario-sc-johnson-pato-gel-adesivo-lavanda-com-6-discos-e-aplicador-1-un/?PID=103831</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Desodorizador Sanitário SC Johnson Pato Gel Adesivo Lavanda com 6 Discos e Aplicador 1 UN</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,41 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1013_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: gel adesivo em discos; o insumo é desodorizador líquido</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1015|1</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/limpa-rejuntes-start-5-litros</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Detergente Desincrustante 5L Limpa Rejuntes - Start</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>70.62</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>59.66</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 59,66 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1015_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1015|2</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>H D DISTRIBUIDORA DE PRODUTOS HIGIENICOS E DESCARTAVEIS LTDA (HD Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>03.868.183/0001-50</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>https://hddistribuidora.com/produto/master-inox-2/</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Detergente Desincrustante Master Inox 5L</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>61.87</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Jadlog Package (Melhor Envio) (5 a 7 dias úteis): R$61,87</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1015_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1018|1</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/esponja-de-aco-q-lustro-14x08x-60g-und</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Esponja De Aço Q Lustro 14x08x 60g Und</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>36.68</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 40,91 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1018_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: fardo 14 x 8 (pacote grande); o insumo é pacote c/ 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1018|2</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/esponja-de-aco-gota-limpa-44g-c-8.html</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Esponja de Aço Gota Limpa 44g c/ 8</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>31.54</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1018_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1020|1</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/fibra-de-limpeza-macia-3m-scotch-brite-profissional-102mm-x-260mm</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Fibra de Limpeza Macia 3M Scotch-Brite Profissional - 102mm x 260mm BRANCA</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>16.52</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 16,52 8 dias úteis Loggi - Express</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1020_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: unidade avulsa; o insumo é pacote c/ 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1021|1</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/fibra-verde-limpeza-geral-102x260mm-superpro</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Fibra Verde Limpeza Geral 102x260mm Superpro</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>31.54</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1021_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: unidade avulsa; o insumo é pacote c/ 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1021|2</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/fibra-de-uso-geral-225x101x11mm-verde</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Fibra de uso geral 260x102mm - Verde - SuperPro (Quantidade: Pacote com 10 unidades)</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>27.42</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 27,42 5 dias úteis Jadlog - .Com</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1021_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>Frete coberto pelo banner no print</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1021|3</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/fibra-de-limpeza-uso-geral-3m-scotch-brite-profissional-102mm-x-260mm</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Fibra de Limpeza Uso Geral 3M Scotch-Brite Profissional - 102mm x 260mm VERDE</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 16,50 8 dias úteis Loggi - Express</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1021_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: unidade avulsa; o insumo é pacote c/ 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1022|1</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto//flanela-28x38cm-laranja.html</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>Flanela 28x38cm Laranja</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>28.06</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 11 dias úteis Correios - Mini Envios</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1022_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: flanela 28 x 38 cm; o insumo é aproximadamente 40 x 60 cm (fora da tolerância de 10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1024|1</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/palha-de-aco-grossa-n-2-brillo</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>Palha de Aço Grossa nº 2 - Brillo</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>27.42</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 27,42 5 dias úteis Jadlog - .Com</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1024_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1028|1</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/limpador-multiuso-pronto-uso-soft-pig-foam-500-ml-dub-boyz</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Limpador Multiuso Pronto Uso Soft Pig Foam 500 ml - Dub Boyz</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>24.16</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>40.78</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 40,78 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1028_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1032|1</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>01.974.824/0001-25</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br/pano-de-chao-40x70cm-enxuga-65gr-1977-p140403</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Pano de Chão 40x70cm Enxuga 65gr</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>21.62</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 21,62 5 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1032_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: pano 40 x 70 cm; o insumo é aproximadamente 60 x 80 cm (fora da tolerância de 10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1033|1</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/panos-de-limpeza/pano-de-prato-caebitex-copa-bainha-40x65cm-estampado-1-un/?PID=162884</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Pano de Prato Caebitex Copa Bainha 40x65cm Estampado 1 UN</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>30.16</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 30,16 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1033_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: pano estampado; o insumo é pano de prato branco</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1035|1</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/produto//papel-higienico-rolao-8x200m-folha-dupla-100-cel-seletto.html</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Papel Higiênico Rolão 8x200m Folha Dupla 100%CEL - Seletto</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>101.6</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>60.05</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 60,05 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1035_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: folha dupla, 200 m; o insumo é folha simples, 300 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1035|2</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/papel-higienico-rolao-branco-luxo-suell-8x300m</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Papel Higienico Rolão Branco Luxo Lipp 8x300m</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>40.48</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>49.31</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 49,31 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1035_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>Nome do produto encoberto pelo menu do site no print</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1035|3</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/papel-higienico-folha-simples-bianco-60-metros-x-10cm-mili</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Papel Higiênico Folha Simples - Bianco - (60 metros x 10cm) - Mili (Fragrância: Neutro; Quantidade: 12 rolos)</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>45.85</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 45,85 7 dias úteis Correios - PAC</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1035_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: rolo de 60 m; o insumo é rolão de 300 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1036|1</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/papel-toalha-bob-06x20x200m-100-cel-alavanca-premium-8056-florax.html</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Papel Toalha Bob 06x20x200m 100% Cel Premium 8056 - Florax</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>132.08</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>60.42</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 60,42 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1036_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: papel toalha em bobina; o insumo é interfolhado</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1036|2</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/papel-higienico-interfolhado-cai-cai</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Papel higiênico interfolhado (cai-cai) (Modelo: Folha Dupla; Quantidade: Caixa c/ 10.000 folhas)</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>115.9</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>82.91</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 82,91 7 dias úteis Correios - PAC</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1036_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: papel higiênico interfolhado; o insumo é papel toalha interfolhado</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1036|3</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/toalha-de-papel-interfolha/papel-toalha-ouroppel-interfolhado-folha-simples-pct-c4800-fl/?PID=31885</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Papel Toalha Ouroppel Interfolhado Folha Simples PCT C/4800 FL</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>129.9</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>78.09</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 78,09 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1036_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: pacote c/ 4.800 folhas; o insumo é fardo c/ 1.000 folhas</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1036|4</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/papel-interfolhado-folha-simples-1000-folhas-20x21cm-elite-professional</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Papel Interfolhado Folha Simples 1000 Folhas 20x21cm - Elite Professional</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>19.93</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 19,93 11 dias úteis Jadlog - .Package Centralizado</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1036_GO_4.png</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1038|1</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/sabao-em-barra-glicerinado-neutro-minuano-900g-5-barras</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Sabão em Barra Glicerinado Neutro Minuano 900G 5 barras</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>19.93</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 19,93 15 dias úteis Jadlog - .Package Centralizado</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1038_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1043|1</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/saco-para-lixo-hospitalar-infectante-branco-30-litros-plasticos-jurema</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Saco para Lixo Hospitalar - Infectante - Branco - 30 Litros - Plásticos Jurema</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 29,37 6 dias úteis Jadlog - .Package</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1043_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1043|2</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/sacos-para-lixo/saco-para-lixo-altaplast-super-economico-30l-azul-59x62cm-pct-c50-un/?PID=24818</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Saco para Lixo Altaplast Super Econômico 30L Azul 59x62cm PCT C/50 UN</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>32.66</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 32,66 Prazo: Entrega em até 9 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1043_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: pacote c/ 50; o insumo é pacote c/ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1043|3</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>GUARULHOS DISTRIBUIDORA DE EMBALAGENS LTDA (Guarulhos Embalagens)</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>30.679.614/0001-02</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>https://www.guarulhosembalagens.com.br/produtos-de-limpeza/saco-de-lixo/saco-de-lixo-roll-30l-com-10un</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Saco De Lixo Roll 30L Com 10un</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: CORREIOS PAC R$ 24,10 Previsto para 23/10/2026 até 27/10/2026</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1043_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: rolo c/ 10; o insumo é pacote c/ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1046|1</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/saco-para-lixo-hospitalar-infectante-branco-100-litros-plasticos-jurema</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Saco para Lixo Hospitalar - Infectante - Branco - 100 Litros - Plásticos Jurema</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>38.31</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 38,31 6 dias úteis Jadlog - .Package</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1046_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1046|2</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/l7vwq5qby-saco-para-lixo-60-litros-10-unidades-sineplast</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Saco para Lixo 100 Litros BL 5 10 Unidades - Sineplast</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>16.69</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 16,69 5 dias úteis Loggi - Express</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1046_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: 10 unidades; o insumo é pacote c/ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1048|1</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/saco-para-lixo-preto-200l-c50-resistencia-super-reforcado.html</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Saco de Lixo Preto 200L c/50 Super Reforçado</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>74.38</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>49.13</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 49,13 9 dias úteis Jadlog - .Package</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1048_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: pacote c/ 50; o insumo é pacote c/ 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1048|2</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>K.M COMERCIO DE EMBALAGENS E PRODUTOS DE LIMPEZA LTDA (Casa do Saco de Lixo)</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>02.236.630/0001-95</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>https://loja.casadosacodelixo.com.br/saco-para-lixo-hospitalar-infectante-branco-200-litros-plasticos-jurema</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Saco para Lixo Hospitalar - Infectante - Branco - 200 Litros - Plásticos Jurema</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>38.31</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 38,31 6 dias úteis Jadlog - .Package</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1048_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1051|1</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/base-seladora-05-lt-piso-adhere-interno-quimistar</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Seladora Piso 5L Adhere Interno - Quimistar</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>129.04</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>60.39</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 60,39 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1051_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1051|2</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/selador-termoplastico-5-litros-spartan</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Selador Termoplástico 5 Litros Spartan</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 37,37 9 dias úteis Jadlog Package</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1051_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1053|1</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>HIGIENIZE COMERCIAL LTDA (Higienize)</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>95.054.177/0001-87</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>https://www.higienize.com/produtos-de-limpeza/disco-de-limpeza-3m-para-enceradeira-e-lavadora</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>Disco de Limpeza 3M para Enceradeira e Lavadora</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>114.1</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>30.49</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Total Express Standard R$ 30,49 Previsto para 20/10/2026</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1053_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: disco verde de 51 cm; o insumo é disco branco de 350 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1054|1</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>LIMPEZA E HIGIENE</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/produto/disco-fibra-510mm-preto-removedor-super-pro-bettanin.html</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Disco Fibra 510mm Preto Removedor - Super Pro Bettanin</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>39.34</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 39,34 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1054_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: diâmetro 510 mm; o insumo é 350 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1070|1</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/dispenser-papel-rolao-300/500m-branco-new-classic-nobre.html</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>Dispenser Papel Rolão 300/500m Branco New Classic - Nobre</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>59.14</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 59,14 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1070_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1070|2</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/dispenser-papel-higienico-rolao-300500m-nobre-new-classic</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>Dispenser Papel Higiênico Rolão Nobre New Classic Branco</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>39.98</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>31.54</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1070_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>Nome do produto encoberto pelo menu do site no print</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1070|3</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>VW COMERCIO DE HIDRAULICA E PLASTICOS INDUSTRIAIS LTDA (Plásticos Ipiranga)</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>19.218.815/0001-70</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>https://loja.plasticosipiranga.com.br/dispenser-clean-velox-papel-higienico-rolao-branco</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>Dispenser Clean Velox Papel Higiênico Rolão - Branco</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>73.65</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>34.77</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 34,77 8 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1070_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1072|1</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/dispenser-plastico-p/sabonete-liquido-/alcool-gel</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>Dispenser P/ Sabonete Liq/Alcool Gel 800ml Ref 9702 - Super Pro Bettanin</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>43.04</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>39.26</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 39,26 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1072_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1076|1</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>1076</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/escova-sanitaria-com-pote</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>Escova Sanitária Com Suporte - Rodo 2000</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1076_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1078|1</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/espanador-soft-de-microfibra-kd-d11-nobre</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Espanador soft de microfibra (KD-D11) - Nobre</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>17.57</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 36,64 7 dias úteis Correios PAC</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1078_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1081|1</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/aspirador-de-po/aspirador-de-po-mondial-turbo-cycle-1100w-127v-ap36-vermelho-1-un/?PID=57747</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>Aspirador de Pó Mondial Turbo Cycle 1100W 127V AP-36 Vermelho 1 UN</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>229.8</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>78.73</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 78,73 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1081_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: aspirador doméstico 1100 W; o insumo é aspirador industrial</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1082|1</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/aspirador-de-po-e-agua-60l-ridgid-wd-1855-4850w/p</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>Aspirador de Pó e Água 60L Ridgid WD-1855 4850W</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>4129.9</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>73.24</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Em até 8 dias úteis R$ 73,24</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1082_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: potência de trabalho 1390 W (descrição da página; os 4850 W do nome são de pico); o insumo pede mínimo de 1.600 W (decisão de 14/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1083|1</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-mondial-aqua-power-iii-1800w-220v-lap03gy-cinza-com-amarelo-1-un/?PID=204328</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Lavadora de Alta Pressão Mondial Aqua Power III 1800W 220V LAP-03-GY Cinza com Amarelo 1 UN</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>930.15</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>83.27</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 83,27 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1083_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1083|2</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/enceradeira-linha-c-200-rpm-410mm-bivolt-certec</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Enceradeira Linha C 200 Rpm 410mm Bivolt Certec</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>4641</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1083_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1083|3</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>08.615.223/0001-75</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>https://www.fermarcsferramentas.com.br/ferramentas-e-maquinas/lavadoras-de-alta-pressao/lavadora-j5000-220v-60-50hz-1256895</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>Lavadora J5000 220v 60.50hz 1256895</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>849.9</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1083_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1083|4</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/lavadora-pressao-karcher-585/p</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Lavadora de Alta Pressão Karcher HD 585 Profi</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>2349.9</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>64.43</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Em até 8 dias úteis R$ 64,43</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1083_GO_4.png</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1084|1</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-mondial-aqua-power-iii-1800w-220v-lap03gy-cinza-com-amarelo-1-un/?PID=204328</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Lavadora de Alta Pressão Mondial Aqua Power III 1800W 220V LAP-03-GY Cinza com Amarelo 1 UN</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>930.15</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>83.27</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 83,27 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1084_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1084|2</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>08.615.223/0001-75</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>https://www.fermarcsferramentas.com.br/ferramentas-e-maquinas/lavadoras-de-alta-pressao/lavadora-j5000-220v-60-50hz-1256895</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Lavadora J5000 220v 60.50hz 1256895</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>849.9</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1084_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1085|1</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA (Gimba)</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/lavadoras-de-alta-pressao/lavadora-de-alta-pressao-mondial-aqua-power-i-1400w-220v-lap01gy-cinza-com-amarelo-1-un/?PID=204324</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Lavadora de Alta Pressão Mondial Aqua Power I 1400W 220V LAP-01-GY Cinza com Amarelo 1 UN</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>577.05</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>80.98</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Valor: R$ 80,98 Prazo: Entrega em até 7 dia(s) úteis após liberação do pedido!</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1085_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1085|2</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>08.615.223/0001-75</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>https://www.fermarcsferramentas.com.br/ferramentas-e-maquinas/lavadoras-de-alta-pressao/lavadora-j5000-220v-60-50hz-1256895</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Lavadora J5000 220v 60.50hz 1256895</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>849.9</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1085_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1085|3</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/lavadora-pressao-karcher-585/p</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>Lavadora de Alta Pressão Karcher HD 585 Profi</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>2349.9</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>64.43</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Em até 8 dias úteis R$ 64,43</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1085_GO_3.png</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora de alta pressão; o insumo é enceradeira/lavadora de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1086|1</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Casa do Pica-Pau Ltda</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>50.223.823/0001-54</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>https://www.casadopicapau.com.br/mangueira-polietileno-25mm-3mm-rolo-50m-tramontina/p</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Mangueira Polietileno 25mm x 3mm Rolo de 50m - Tramontina</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>557.33</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1086_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1087|1</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>1087</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Casa do Pica-Pau Ltda</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>50.223.823/0001-54</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>https://www.casadopicapau.com.br/mangueira-polietileno-25mm-3mm-rolo-100m-tramontina/p</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Mangueira Polietileno 25mm x 3mm Rolo de 100m - Tramontina</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>1114.66</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1087_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1088|1</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/pa-de-lixo-jeitosa-canguru-bettanin-56036/p</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>Pá de lixo Jeitosa Canguru Bettanin</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>91.9</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>12.78</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Em até 7 dias úteis R$ 12,78</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1088_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: pá com cabo longo (foto); o insumo é pá com cabo curto</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1093|1</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/1125--rodo-eva-40cm-12x1-57958/p</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>1125 RODO EVA 40CM 12X1</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Em até 7 dias úteis R$ 14,92</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1093_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1094|1</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>LF COMERCIAL DE BENS LTDA (LF Máquinas e Ferramentas)</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>91.845.735/0004-14</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>https://www.lfmaquinaseferramentas.com.br/1128-rodo-60cm-12x1-57947/p</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>1128 RODO 60CM 12X1</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>48.9</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Em até 7 dias úteis R$ 14,92</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1094_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1096|1</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>NC BELLA COMERCIO E DISTRIBUICAO DE EQUIPAMENTOS E MATERIAIS DE LIMPEZA LTDA (NC Bella Distribuidora)</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>57.935.095/0001-52</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>https://www.ncbelladistribuidora.com.br/rodo-de-plastico-com-borracha-dupla-55-cm-sem-cabo-certec</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Rodo de Plástico com Borracha Dupla 55 cm Sem Cabo – Certec</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>17.15</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 17,15 8 dias úteis Loggi - Express</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1096_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: rodo de piso sem cabo; o insumo é rodo para vidros com cabo extensível</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1096|2</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Fermarcs Comércio Varejista de Ferramentas e Acessórios Ltda</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>08.615.223/0001-75</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>https://www.fermarcsferramentas.com.br/casa-e-lazer/limpeza/rodo-plastico-40cm-cabo-verde</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Rodo Plastico 40cm + Cabo Verde</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>51.59</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Transportadora Do Valle R$ 51,59 2 a 4 dia(as) (16/10/2026 até 20/10/2026). Avisos:</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1096_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: rodo de piso; o insumo é rodo para vidros com cabo extensível (o produto já está no 1093)</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1097|1</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>PLAST HOUSE LTDA (Plast House)</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>52.081.713/0001-20</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>https://plasthouse.com.br/produto/casa/cozinha/outrios-itens-de-cozinha/rodo-de-pia-sanremo/</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Rodo de Pia - Sanremo</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>28.85</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JeT Standard (Melhor Envio) (11 a 13 dias úteis): R$ 28,85</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1097_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1098|1</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>01.974.824/0001-25</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br/vassoura-super-tupy-cerdas-longas-com-cabo-120mt-2075-p140926</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Vassoura Super Tupy Cerdas Longas Com Cabo 1,20mt</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>33.90</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>22.76</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 22,76 5 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1098_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1103|1</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>01.974.824/0001-25</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br/vassoura-tira-po-limpa-teto-forro-e-gesso-1982-p140450</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Vassoura Tira Pó Limpa Teto Forro e Gesso</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>21.62</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 21,62 5 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1103_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: a página mostra só a cabeça da vassoura (sem cabo) e cerdas que parecem naturais; o insumo pede cerdas de nylon e cabo longo (decisão de 14/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1104|1</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/uniforme/camisa-azul-royal-manga-longa-em-brim-com-gola-italiana-e-refletivo?variant_id=4211</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Camisa Azul Royal Manga Longa em Brim com Gola Italiana e Refletivo</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>90.24</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1104_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: camisa de brim com gola italiana; o insumo é camiseta de malha fria, gola redonda/esporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1104|2</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>COMERCIAL DE REFRIGERACAO PANAN OESTE LTDA (Panan)</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>15.448.996/0001-70</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>https://www.panan.com.br/pecas-e-epi/avental-e-camiseta/camiseta-profissional-branca-gg-para-cozinha-e-trabalho-em-poliester</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Camiseta Profissional Branca GG para Cozinha e Trabalho em Poliéster.</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>73.09</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 73,09 7 a 9 dias úteis</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1104_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1105|1</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/uniforme/calca-em-brim-azul-royal-com-elastico-total-e-refletivo?variant_id=4175</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>Calça em Brim Azul Royal com Elástico total e Refletivo</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>78.42</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1105_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>Preço encoberto pelo menu do site no print</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1106|1</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/meiao-futebol-treino-profissional-algodao</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Meião Futebol Treino Profissional Algodão</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1106_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>Nome do produto encoberto pelo menu do site no print; print só mostra o preço com PIX/boleto</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1106|2</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>14.213.841/0001-91</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>https://www.trepis.com.br/c-a-41555-meiao-de-algodao-cru-modelo-tubular-atoalhado-riscos-termicos-frio</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Meião de Algodão Cru Térmico Tubular Atoalhado CA 41555</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>11.93</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1106_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: meião cor crua; o insumo é meia preta ou azul</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1109|1</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/luva-de-pvc-forrada-palma-aspera-plastcor-45cm-ca-34570</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>LUVA PVC HANDEX PALMA ASPERA 46CM</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>26.78</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1109_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>Nome do produto encoberto pelo menu do site no print; print só mostra o preço com PIX/boleto</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1110|1</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/luva-de-latex-kalipso-amarela-ca-13959</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>Luva de Látex Multiuso Kalipso Amarela CA13959 (Tamanho: P)</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>4.69</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1110_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1112|1</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>31.893.116/0001-20</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>https://www.loja.bhzepi.com.br/luva-de-segurana-malha-tricotada-pigmentada-branca</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>Luva De Segurança Malha Tricotada Pigmentada branca</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>20.62</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1112_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1112|2</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-tricotada-cru-com-6-fios-pigmentada-branca-c-a-31909</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Luva Tricotada Cru Com 6 Fios Pigmentada Branca | C.A. 31909</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1112_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>Preço encoberto pelo menu do site no print</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1113|1</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>20.838.307/0001-73</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>https://www.lojadoepi.com.br/oculos-de-protecao-vvision-600-incolor-antiembacante-volk-ca-42922-p3187</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Óculos de Proteção Vvision 600 Incolor Antiembaçante Volk CA 42922</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>21.39</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39 7 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1113_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1114|1</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>ASTRO DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>18.597.685/0001-60</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>https://www.astrodistribuidora.com/mascara-de-tnt-descartavel-com-elastico-volk</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Máscara de TNT Descartável com Elástico - Volk (100 Unidades)</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>10.42</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>26.82</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$26,82 BRASPRESS - Entrega em até 15 dias úteis -</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1114_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1114|2</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>14.213.841/0001-91</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>https://www.trepis.com.br/mascara-descartavel-confec-em-tnt-tripla-branca-com-elastico-pct-c50un</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>Máscara Descartável Tripla TNT Branca com Elástico Pacote com 50 Unidades</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>10.81</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1114_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1117|1</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>31.893.116/0001-20</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>https://www.loja.bhzepi.com.br/produto/capa-de-chuva-pvc-amarelo-forrado-tamanho-g.html</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Capa De Chuva Pvc Amarelo Forrado Tamanho G</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>20.62</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1117_GO_1.png</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>R|2026-10-14_105308|1117|2</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Robô 2026-10-14_105308</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/produto/capa-de-chuva-policap-pvc-forrado-azul.html</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Capa de Chuva Policap PVC Forrado Azul (Tamanho: M)</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>36.99</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,44 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>prints_candidatos/robo_2026-10-14_105308/1117_GO_2.png</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R496"/>
+  <autoFilter ref="A1:R579"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/_historico/merge/candidatos.xlsx
+++ b/_historico/merge/candidatos.xlsx
@@ -1319,6 +1319,11 @@
           <t>49.4</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>52.00</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>74.85</t>
@@ -1336,7 +1341,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -1478,6 +1483,11 @@
           <t>113.88</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>117.40</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>36.1</t>
@@ -1495,7 +1505,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1890,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: a descrição diz "Comprimento: 26cm" (cano curto); o insumo pede cano médio ou longo (decisão de 14/10/2026)</t>
         </is>
       </c>
     </row>
@@ -3227,6 +3242,11 @@
           <t>16.9</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>16.10</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>frete nao calculado: fornecedor com sede em GO</t>
@@ -3239,7 +3259,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3336,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Print reduzido: nome, preço e frete ilegíveis</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3418,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Frete coberto pelo banner de cookies no print</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3500,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Nome do produto encoberto pelo menu do site no print</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3577,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4131,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5935,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6176,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10251,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11220,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11461,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13896,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14055,12 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>CEP não preenchido: frete não aparece no print</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16259,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -16296,7 +16336,12 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: papel higiênico interfolhado (cai-cai), sem rolo; o insumo pede metragem por rolo (decisão de 14/10/2026)</t>
         </is>
       </c>
     </row>
@@ -18567,7 +18612,12 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: sabonete antisséptico "Sem Aroma" (rótulo); o insumo é sabonete com fragrância</t>
         </is>
       </c>
     </row>
@@ -21740,7 +21790,7 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24687,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -25455,6 +25505,11 @@
           <t>1114.44</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>1173.10</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>236.52</t>
@@ -25472,7 +25527,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -30365,7 +30420,12 @@
       </c>
       <c r="P368" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Produto não corresponde: lavadora para serviços domésticos (descrição da página); o insumo é de uso profissional</t>
         </is>
       </c>
     </row>
@@ -30673,7 +30733,7 @@
       </c>
       <c r="P372" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -34286,7 +34346,12 @@
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Print só mostra o preço com desconto ("Por R$ 32,87" com 5% no boleto/PIX já aplicado); o preço lido (40,71) é o "De" riscado</t>
         </is>
       </c>
     </row>
@@ -34363,7 +34428,7 @@
       </c>
       <c r="P417" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
@@ -34505,6 +34570,11 @@
           <t>55.81</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>55.81</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>20.49</t>
@@ -34522,7 +34592,7 @@
       </c>
       <c r="P419" t="inlineStr">
         <is>
-          <t>A REVISAR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>

--- a/_historico/merge/candidatos.xlsx
+++ b/_historico/merge/candidatos.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidatos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatos'!$A$1:$R$579</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatos'!$A$1:$R$581</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R579"/>
+  <dimension ref="A1:R581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -47181,7 +47181,12 @@
       </c>
       <c r="P576" t="inlineStr">
         <is>
-          <t>APROVADO</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>Pacote de várias unidades num insumo vendido por unidade (o preço não é o da unidade). Apontado pelo William em 15/10/2026.</t>
         </is>
       </c>
     </row>
@@ -47258,7 +47263,12 @@
       </c>
       <c r="P577" t="inlineStr">
         <is>
-          <t>APROVADO</t>
+          <t>REPROVADO</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>Pacote de várias unidades num insumo vendido por unidade (o preço não é o da unidade). Apontado pelo William em 15/10/2026.</t>
         </is>
       </c>
     </row>
@@ -47416,8 +47426,167 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>L|2026-10-16_065027|1</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Coleta por link 2026-10-16_065027</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Mais Segurança EPI</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>43.903.641/0001-69</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>https://maisseguranca.online/#/produto-detalhes/nUNEWOBUivWtuxf5g7uS3ulpNCn2/-N4ce5UWWtjnB32sQoGd</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>SAPATO IMPERMEAVEL ANTIDERRAPANTE PRETO MAN 41 - STICKY SHOES CA.39674</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>78.00</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Frete não calculado (GO para GO)</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>coleta_links/2026-10-16_065027/prints/001_1107.png</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Print revisado em 16/10/2026: nome e preço (R$ 78,00) visíveis; GO. Sapato = calçado e "impermeável"/"antiderrapante" no nome (decisão da Tamirys, 16/10). O tamanho 41 mostra estoque 0, mas o produto tem estoque (ESTQ 7).</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>O aviso de aderência era anterior à mudança de 16/10 (sapato = calçado); o nome passa na regra atual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>L|2026-10-16_065027|2</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Coleta por link 2026-10-16_065027</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Mais Segurança EPI</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>43.903.641/0001-69</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>https://maisseguranca.online/#/produto-detalhes/nUNEWOBUivWtuxf5g7uS3ulpNCn2/-NWsT-o_-VgTH2z0Xn2v</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>RESPIRADOR PFF2 AZ S/VALV PRO SAFETY - DELTA PLUS CA.38504</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>Frete não calculado (GO para GO)</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>coleta_links/2026-10-16_065027/prints/002_1114.png</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>APROVADO</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>Print revisado em 16/10/2026: nome e preço (R$ 1,00) visíveis; GO. Página: respirador descartável, embalado individualmente (venda por unidade). PFF2 aceito como máscara descartável (Tamirys, 16/10).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R579"/>
+  <autoFilter ref="A1:R581"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>